--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01B.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODE\GIT\TTBC_NEW\IMS_REPORTS\web\EXCEL_TEMPLATE\KHNV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443C56B2-34B7-41A4-B312-9D896A75E017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA727D44-7FEC-482A-83C3-9A374F2D8B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30211,7 +30211,6 @@
       <c r="D994" s="90"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="GcPJzn8RrpvD+90LQSmR8MD/W9PkZn8BD2CnCppZj8+ABvweRSt+1lV0rjXmYfDY29lFBJERawAj8iHhkVtCRw==" saltValue="km17jyYtlxuXjvqvUtX45A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="5">
     <mergeCell ref="FU1:FX1"/>
     <mergeCell ref="B7:B8"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01B.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_DK01B.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source_tree\IMS_REPORTS\build\web\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Son Nguyen\Desktop\Zalo đến\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59B5F15-BD41-4BF0-A8CD-B008303DBC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,13 +34,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
     <author>Son Nguyen</author>
   </authors>
   <commentList>
-    <comment ref="E8" authorId="0" shapeId="0">
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -55,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0">
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -71,7 +72,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C38" authorId="1" shapeId="0">
+    <comment ref="C38" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -96,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C42" authorId="1" shapeId="0">
+    <comment ref="C42" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C88" authorId="1" shapeId="0">
+    <comment ref="C88" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -145,7 +146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C91" authorId="1" shapeId="0">
+    <comment ref="C91" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -169,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C94" authorId="1" shapeId="0">
+    <comment ref="C94" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -208,9 +209,6 @@
     <t>Biểu số: 01/NHCS-KH</t>
   </si>
   <si>
-    <t>NHU CẦU VỐN TÍN DỤNG CHÍNH SÁCH NĂM …</t>
-  </si>
-  <si>
     <t>XÃ/PHƯỜNG/THỊ TRẤN: ……………………………………</t>
   </si>
   <si>
@@ -1297,12 +1295,15 @@
   </si>
   <si>
     <t>XD000251</t>
+  </si>
+  <si>
+    <t>NHU CẦU VỐN TÍN DỤNG CHÍNH SÁCH NĂM 2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="26">
     <font>
       <sz val="11"/>
@@ -2435,7 +2436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:FX993"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -2996,7 +2997,7 @@
     <row r="4" spans="1:180" ht="18.75" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="8" t="s">
-        <v>1</v>
+        <v>363</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -3180,7 +3181,7 @@
     <row r="5" spans="1:180" ht="14.4">
       <c r="A5" s="1"/>
       <c r="B5" s="11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
@@ -3364,7 +3365,7 @@
     <row r="6" spans="1:180" ht="16.8">
       <c r="A6" s="1"/>
       <c r="B6" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -3548,16 +3549,16 @@
     <row r="7" spans="1:180" ht="15.6">
       <c r="A7" s="15"/>
       <c r="B7" s="127" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="127" t="s">
+      <c r="D7" s="127" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="127" t="s">
+      <c r="E7" s="130" t="s">
         <v>6</v>
-      </c>
-      <c r="E7" s="130" t="s">
-        <v>7</v>
       </c>
       <c r="F7" s="131"/>
       <c r="G7" s="131"/>
@@ -4457,558 +4458,558 @@
     </row>
     <row r="10" spans="1:180" ht="14.4">
       <c r="A10" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="C10" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="D10" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="E10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="F10" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="G10" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="H10" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="I10" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="J10" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="K10" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="22" t="s">
+      <c r="L10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="M10" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="N10" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="N10" s="22" t="s">
+      <c r="O10" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="19" t="s">
+      <c r="P10" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="P10" s="19" t="s">
+      <c r="Q10" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="Q10" s="22" t="s">
+      <c r="R10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="R10" s="19" t="s">
+      <c r="S10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="S10" s="19" t="s">
+      <c r="T10" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="T10" s="22" t="s">
+      <c r="U10" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="U10" s="19" t="s">
+      <c r="V10" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="V10" s="19" t="s">
+      <c r="W10" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="W10" s="22" t="s">
+      <c r="X10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="X10" s="19" t="s">
+      <c r="Y10" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Y10" s="19" t="s">
+      <c r="Z10" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="Z10" s="22" t="s">
+      <c r="AA10" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="AA10" s="19" t="s">
+      <c r="AB10" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="AB10" s="19" t="s">
+      <c r="AC10" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="AC10" s="22" t="s">
+      <c r="AD10" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="AD10" s="19" t="s">
+      <c r="AE10" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="AE10" s="19" t="s">
+      <c r="AF10" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="AF10" s="22" t="s">
+      <c r="AG10" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="AG10" s="19" t="s">
+      <c r="AH10" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="AH10" s="19" t="s">
+      <c r="AI10" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="AI10" s="22" t="s">
+      <c r="AJ10" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="AJ10" s="19" t="s">
+      <c r="AK10" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="AK10" s="19" t="s">
+      <c r="AL10" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="AL10" s="22" t="s">
+      <c r="AM10" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="AM10" s="19" t="s">
+      <c r="AN10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="AN10" s="19" t="s">
+      <c r="AO10" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="AO10" s="22" t="s">
+      <c r="AP10" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AP10" s="19" t="s">
+      <c r="AQ10" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="AQ10" s="19" t="s">
+      <c r="AR10" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="AR10" s="22" t="s">
+      <c r="AS10" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="AS10" s="19" t="s">
+      <c r="AT10" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="AT10" s="19" t="s">
+      <c r="AU10" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="AU10" s="22" t="s">
+      <c r="AV10" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AV10" s="19" t="s">
+      <c r="AW10" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AW10" s="19" t="s">
+      <c r="AX10" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="AX10" s="22" t="s">
+      <c r="AY10" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="AY10" s="19" t="s">
+      <c r="AZ10" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="AZ10" s="19" t="s">
+      <c r="BA10" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="BA10" s="22" t="s">
+      <c r="BB10" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="BB10" s="19" t="s">
+      <c r="BC10" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="BC10" s="19" t="s">
+      <c r="BD10" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="BD10" s="22" t="s">
+      <c r="BE10" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="BE10" s="19" t="s">
+      <c r="BF10" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="BF10" s="19" t="s">
+      <c r="BG10" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="BG10" s="22" t="s">
+      <c r="BH10" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="BH10" s="19" t="s">
+      <c r="BI10" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="BI10" s="19" t="s">
+      <c r="BJ10" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="BJ10" s="22" t="s">
+      <c r="BK10" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="BK10" s="19" t="s">
+      <c r="BL10" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="BL10" s="19" t="s">
+      <c r="BM10" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="BM10" s="22" t="s">
+      <c r="BN10" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="BN10" s="19" t="s">
+      <c r="BO10" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="BO10" s="19" t="s">
+      <c r="BP10" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="BP10" s="22" t="s">
+      <c r="BQ10" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="BQ10" s="19" t="s">
+      <c r="BR10" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="BR10" s="19" t="s">
+      <c r="BS10" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="BS10" s="22" t="s">
+      <c r="BT10" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="BT10" s="19" t="s">
+      <c r="BU10" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="BU10" s="19" t="s">
+      <c r="BV10" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="BV10" s="22" t="s">
+      <c r="BW10" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="BW10" s="19" t="s">
+      <c r="BX10" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="BX10" s="19" t="s">
+      <c r="BY10" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="BY10" s="22" t="s">
+      <c r="BZ10" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="BZ10" s="19" t="s">
+      <c r="CA10" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="CA10" s="19" t="s">
+      <c r="CB10" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="CB10" s="22" t="s">
+      <c r="CC10" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="CC10" s="19" t="s">
+      <c r="CD10" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="CD10" s="19" t="s">
+      <c r="CE10" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="CE10" s="22" t="s">
+      <c r="CF10" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="CF10" s="19" t="s">
+      <c r="CG10" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="CG10" s="19" t="s">
+      <c r="CH10" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="CH10" s="22" t="s">
+      <c r="CI10" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="CI10" s="19" t="s">
+      <c r="CJ10" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="CJ10" s="19" t="s">
+      <c r="CK10" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="CK10" s="22" t="s">
+      <c r="CL10" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="CL10" s="19" t="s">
+      <c r="CM10" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="CM10" s="19" t="s">
+      <c r="CN10" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="CN10" s="22" t="s">
+      <c r="CO10" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="CO10" s="19" t="s">
+      <c r="CP10" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="CP10" s="19" t="s">
+      <c r="CQ10" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="CQ10" s="22" t="s">
+      <c r="CR10" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="CR10" s="19" t="s">
+      <c r="CS10" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="CS10" s="19" t="s">
+      <c r="CT10" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="CT10" s="22" t="s">
+      <c r="CU10" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="CU10" s="19" t="s">
+      <c r="CV10" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="CV10" s="19" t="s">
+      <c r="CW10" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="CW10" s="22" t="s">
+      <c r="CX10" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="CX10" s="19" t="s">
+      <c r="CY10" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="CY10" s="19" t="s">
+      <c r="CZ10" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="CZ10" s="22" t="s">
+      <c r="DA10" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="DA10" s="19" t="s">
+      <c r="DB10" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="DB10" s="19" t="s">
+      <c r="DC10" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="DC10" s="22" t="s">
+      <c r="DD10" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="DD10" s="19" t="s">
+      <c r="DE10" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="DE10" s="19" t="s">
+      <c r="DF10" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="DF10" s="22" t="s">
+      <c r="DG10" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="DG10" s="19" t="s">
+      <c r="DH10" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="DH10" s="19" t="s">
+      <c r="DI10" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="DI10" s="22" t="s">
+      <c r="DJ10" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="DJ10" s="19" t="s">
+      <c r="DK10" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="DK10" s="19" t="s">
+      <c r="DL10" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="DL10" s="22" t="s">
+      <c r="DM10" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="DM10" s="19" t="s">
+      <c r="DN10" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="DN10" s="19" t="s">
+      <c r="DO10" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="DO10" s="22" t="s">
+      <c r="DP10" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="DP10" s="19" t="s">
+      <c r="DQ10" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="DQ10" s="19" t="s">
+      <c r="DR10" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="DR10" s="22" t="s">
+      <c r="DS10" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="DS10" s="19" t="s">
+      <c r="DT10" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="DT10" s="19" t="s">
+      <c r="DU10" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="DU10" s="22" t="s">
+      <c r="DV10" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="DV10" s="19" t="s">
+      <c r="DW10" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="DW10" s="19" t="s">
+      <c r="DX10" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="DX10" s="22" t="s">
+      <c r="DY10" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="DY10" s="19" t="s">
+      <c r="DZ10" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="DZ10" s="19" t="s">
+      <c r="EA10" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="EA10" s="22" t="s">
+      <c r="EB10" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="EB10" s="19" t="s">
+      <c r="EC10" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="EC10" s="19" t="s">
+      <c r="ED10" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="ED10" s="22" t="s">
+      <c r="EE10" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="EE10" s="19" t="s">
+      <c r="EF10" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="EF10" s="19" t="s">
+      <c r="EG10" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="EG10" s="22" t="s">
+      <c r="EH10" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="EH10" s="19" t="s">
+      <c r="EI10" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="EI10" s="19" t="s">
+      <c r="EJ10" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="EJ10" s="22" t="s">
+      <c r="EK10" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="EK10" s="19" t="s">
+      <c r="EL10" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="EL10" s="19" t="s">
+      <c r="EM10" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="EM10" s="22" t="s">
+      <c r="EN10" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="EN10" s="19" t="s">
+      <c r="EO10" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="EO10" s="19" t="s">
+      <c r="EP10" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="EP10" s="22" t="s">
+      <c r="EQ10" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="EQ10" s="19" t="s">
+      <c r="ER10" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="ER10" s="19" t="s">
+      <c r="ES10" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="ES10" s="22" t="s">
+      <c r="ET10" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="ET10" s="19" t="s">
+      <c r="EU10" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="EU10" s="19" t="s">
+      <c r="EV10" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="EV10" s="22" t="s">
+      <c r="EW10" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="EW10" s="19" t="s">
+      <c r="EX10" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="EX10" s="19" t="s">
+      <c r="EY10" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="EY10" s="22" t="s">
+      <c r="EZ10" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="EZ10" s="19" t="s">
+      <c r="FA10" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="FA10" s="19" t="s">
+      <c r="FB10" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="FB10" s="22" t="s">
+      <c r="FC10" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="FC10" s="19" t="s">
+      <c r="FD10" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="FD10" s="19" t="s">
+      <c r="FE10" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="FE10" s="22" t="s">
+      <c r="FF10" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="FF10" s="19" t="s">
+      <c r="FG10" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="FG10" s="19" t="s">
+      <c r="FH10" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="FH10" s="22" t="s">
+      <c r="FI10" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="FI10" s="19" t="s">
+      <c r="FJ10" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="FJ10" s="19" t="s">
+      <c r="FK10" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="FK10" s="22" t="s">
+      <c r="FL10" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="FL10" s="19" t="s">
+      <c r="FM10" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="FM10" s="19" t="s">
+      <c r="FN10" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="FN10" s="22" t="s">
+      <c r="FO10" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="FO10" s="23" t="s">
+      <c r="FP10" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="FP10" s="23" t="s">
+      <c r="FQ10" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="FQ10" s="23" t="s">
+      <c r="FR10" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="FR10" s="23" t="s">
+      <c r="FS10" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="FS10" s="23" t="s">
+      <c r="FT10" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="FT10" s="23" t="s">
+      <c r="FU10" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="FU10" s="23" t="s">
+      <c r="FV10" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="FV10" s="23" t="s">
+      <c r="FW10" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="FW10" s="23" t="s">
+      <c r="FX10" s="23" t="s">
         <v>186</v>
-      </c>
-      <c r="FX10" s="23" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:180" ht="14.4">
       <c r="A11" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="C11" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>190</v>
-      </c>
       <c r="D11" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E11" s="118"/>
       <c r="F11" s="118"/>
@@ -5189,11 +5190,11 @@
     </row>
     <row r="12" spans="1:180" ht="15.6">
       <c r="A12" s="28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D12" s="30">
         <f t="shared" ref="D12:AI12" si="0">D13+D58</f>
@@ -5906,13 +5907,13 @@
     </row>
     <row r="13" spans="1:180" ht="15.6">
       <c r="A13" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="C13" s="36" t="s">
         <v>194</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>195</v>
       </c>
       <c r="D13" s="37">
         <f t="shared" ref="D13:AI13" si="6">D14+D52</f>
@@ -6625,13 +6626,13 @@
     </row>
     <row r="14" spans="1:180" ht="15.6">
       <c r="A14" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="C14" s="42" t="s">
         <v>197</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>198</v>
       </c>
       <c r="D14" s="43">
         <f t="shared" ref="D14:AI14" si="12">SUM(D15:D43)+D51-D37-D22</f>
@@ -7344,13 +7345,13 @@
     </row>
     <row r="15" spans="1:180" ht="15.6">
       <c r="A15" s="46" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B15" s="47">
         <v>1</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D15" s="49">
         <f t="shared" ref="D15:D42" si="18">SUM(E15:FX15)</f>
@@ -7535,13 +7536,13 @@
     </row>
     <row r="16" spans="1:180" ht="15.6">
       <c r="A16" s="46" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B16" s="47">
         <v>2</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D16" s="49">
         <f t="shared" si="18"/>
@@ -7726,13 +7727,13 @@
     </row>
     <row r="17" spans="1:180" ht="15.6">
       <c r="A17" s="46" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" s="47">
         <v>3</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D17" s="49">
         <f t="shared" si="18"/>
@@ -7917,13 +7918,13 @@
     </row>
     <row r="18" spans="1:180" ht="15.6">
       <c r="A18" s="46" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B18" s="47">
         <v>4</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D18" s="49">
         <f t="shared" si="18"/>
@@ -8108,13 +8109,13 @@
     </row>
     <row r="19" spans="1:180" ht="31.2">
       <c r="A19" s="46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B19" s="47">
         <v>5</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D19" s="49">
         <f t="shared" si="18"/>
@@ -8299,13 +8300,13 @@
     </row>
     <row r="20" spans="1:180" ht="46.8">
       <c r="A20" s="46" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B20" s="47">
         <v>6</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D20" s="49">
         <f t="shared" si="18"/>
@@ -8490,13 +8491,13 @@
     </row>
     <row r="21" spans="1:180" ht="15.75" customHeight="1">
       <c r="A21" s="46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B21" s="47">
         <v>7</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D21" s="49">
         <f t="shared" si="18"/>
@@ -8681,13 +8682,13 @@
     </row>
     <row r="22" spans="1:180" ht="15.75" customHeight="1">
       <c r="A22" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="B22" s="52" t="s">
         <v>213</v>
       </c>
-      <c r="B22" s="52" t="s">
+      <c r="C22" s="53" t="s">
         <v>214</v>
-      </c>
-      <c r="C22" s="53" t="s">
-        <v>215</v>
       </c>
       <c r="D22" s="49">
         <f t="shared" si="18"/>
@@ -8872,13 +8873,13 @@
     </row>
     <row r="23" spans="1:180" ht="15.75" customHeight="1">
       <c r="A23" s="46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B23" s="47">
         <v>8</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" s="49">
         <f t="shared" si="18"/>
@@ -9063,13 +9064,13 @@
     </row>
     <row r="24" spans="1:180" ht="15.75" customHeight="1">
       <c r="A24" s="46" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B24" s="47">
         <v>9</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D24" s="49">
         <f t="shared" si="18"/>
@@ -9254,13 +9255,13 @@
     </row>
     <row r="25" spans="1:180" ht="15.75" customHeight="1">
       <c r="A25" s="46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B25" s="47">
         <v>10</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D25" s="49">
         <f t="shared" si="18"/>
@@ -9445,13 +9446,13 @@
     </row>
     <row r="26" spans="1:180" ht="15.75" customHeight="1">
       <c r="A26" s="46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B26" s="47">
         <v>11</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D26" s="49">
         <f t="shared" si="18"/>
@@ -9636,13 +9637,13 @@
     </row>
     <row r="27" spans="1:180" ht="15.75" customHeight="1">
       <c r="A27" s="46" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B27" s="47">
         <v>12</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D27" s="49">
         <f t="shared" si="18"/>
@@ -9827,13 +9828,13 @@
     </row>
     <row r="28" spans="1:180" ht="15.75" customHeight="1">
       <c r="A28" s="46" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B28" s="47">
         <v>13</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D28" s="49">
         <f t="shared" si="18"/>
@@ -10018,13 +10019,13 @@
     </row>
     <row r="29" spans="1:180" ht="15.75" customHeight="1">
       <c r="A29" s="46" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B29" s="47">
         <v>14</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D29" s="49">
         <f t="shared" si="18"/>
@@ -10209,13 +10210,13 @@
     </row>
     <row r="30" spans="1:180" ht="15.75" customHeight="1">
       <c r="A30" s="46" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B30" s="47">
         <v>15</v>
       </c>
       <c r="C30" s="48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D30" s="49">
         <f t="shared" si="18"/>
@@ -10400,13 +10401,13 @@
     </row>
     <row r="31" spans="1:180" ht="15.75" customHeight="1">
       <c r="A31" s="46" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B31" s="47">
         <v>16</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D31" s="49">
         <f t="shared" si="18"/>
@@ -10591,13 +10592,13 @@
     </row>
     <row r="32" spans="1:180" ht="15.75" customHeight="1">
       <c r="A32" s="46" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B32" s="47">
         <v>17</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D32" s="49">
         <f t="shared" si="18"/>
@@ -10782,13 +10783,13 @@
     </row>
     <row r="33" spans="1:180" ht="15.75" customHeight="1">
       <c r="A33" s="46" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B33" s="47">
         <v>18</v>
       </c>
       <c r="C33" s="51" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D33" s="49">
         <f t="shared" si="18"/>
@@ -10973,13 +10974,13 @@
     </row>
     <row r="34" spans="1:180" ht="15.75" customHeight="1">
       <c r="A34" s="46" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B34" s="47">
         <v>19</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D34" s="49">
         <f t="shared" si="18"/>
@@ -11164,13 +11165,13 @@
     </row>
     <row r="35" spans="1:180" ht="15.75" customHeight="1">
       <c r="A35" s="46" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B35" s="47">
         <v>20</v>
       </c>
       <c r="C35" s="55" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D35" s="49">
         <f t="shared" si="18"/>
@@ -11355,13 +11356,13 @@
     </row>
     <row r="36" spans="1:180" ht="15.75" customHeight="1">
       <c r="A36" s="46" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B36" s="47">
         <v>21</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D36" s="49">
         <f t="shared" si="18"/>
@@ -11546,13 +11547,13 @@
     </row>
     <row r="37" spans="1:180" ht="15.75" customHeight="1">
       <c r="A37" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="B37" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="56" t="s">
         <v>244</v>
-      </c>
-      <c r="B37" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="C37" s="56" t="s">
-        <v>245</v>
       </c>
       <c r="D37" s="49">
         <f t="shared" si="18"/>
@@ -11737,11 +11738,11 @@
     </row>
     <row r="38" spans="1:180" ht="15.75" customHeight="1">
       <c r="A38" s="46" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B38" s="52"/>
       <c r="C38" s="120" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D38" s="49">
         <f t="shared" si="18"/>
@@ -11926,13 +11927,13 @@
     </row>
     <row r="39" spans="1:180" ht="15.75" customHeight="1">
       <c r="A39" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="B39" s="47">
+        <v>22</v>
+      </c>
+      <c r="C39" s="51" t="s">
         <v>246</v>
-      </c>
-      <c r="B39" s="47">
-        <v>23</v>
-      </c>
-      <c r="C39" s="51" t="s">
-        <v>247</v>
       </c>
       <c r="D39" s="49">
         <f t="shared" si="18"/>
@@ -12117,13 +12118,13 @@
     </row>
     <row r="40" spans="1:180" ht="15.75" customHeight="1">
       <c r="A40" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="B40" s="47">
+        <v>23</v>
+      </c>
+      <c r="C40" s="55" t="s">
         <v>248</v>
-      </c>
-      <c r="B40" s="47">
-        <v>24</v>
-      </c>
-      <c r="C40" s="55" t="s">
-        <v>249</v>
       </c>
       <c r="D40" s="49">
         <f t="shared" si="18"/>
@@ -12308,13 +12309,13 @@
     </row>
     <row r="41" spans="1:180" ht="15.75" customHeight="1">
       <c r="A41" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="B41" s="47">
+        <v>24</v>
+      </c>
+      <c r="C41" s="55" t="s">
         <v>250</v>
-      </c>
-      <c r="B41" s="47">
-        <v>25</v>
-      </c>
-      <c r="C41" s="55" t="s">
-        <v>251</v>
       </c>
       <c r="D41" s="49">
         <f t="shared" si="18"/>
@@ -12499,11 +12500,13 @@
     </row>
     <row r="42" spans="1:180" ht="15.75" customHeight="1">
       <c r="A42" s="46" t="s">
-        <v>362</v>
-      </c>
-      <c r="B42" s="47"/>
+        <v>361</v>
+      </c>
+      <c r="B42" s="47">
+        <v>25</v>
+      </c>
       <c r="C42" s="121" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D42" s="49">
         <f t="shared" si="18"/>
@@ -12688,13 +12691,13 @@
     </row>
     <row r="43" spans="1:180" ht="15.75" customHeight="1">
       <c r="A43" s="57" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B43" s="47">
         <v>26</v>
       </c>
       <c r="C43" s="48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D43" s="58">
         <f t="shared" ref="D43:FX43" si="19">D44+D45+D46+D47+D48+D49+D50</f>
@@ -13407,13 +13410,13 @@
     </row>
     <row r="44" spans="1:180" ht="15.75" customHeight="1">
       <c r="A44" s="46" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" s="60" t="s">
         <v>254</v>
       </c>
-      <c r="B44" s="60" t="s">
+      <c r="C44" s="61" t="s">
         <v>255</v>
-      </c>
-      <c r="C44" s="61" t="s">
-        <v>256</v>
       </c>
       <c r="D44" s="62">
         <f t="shared" ref="D44:D51" si="20">SUM(E44:FX44)</f>
@@ -13598,11 +13601,11 @@
     </row>
     <row r="45" spans="1:180" ht="15.75" customHeight="1">
       <c r="A45" s="46" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B45" s="63"/>
       <c r="C45" s="61" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D45" s="62">
         <f t="shared" si="20"/>
@@ -13787,11 +13790,11 @@
     </row>
     <row r="46" spans="1:180" ht="15.75" customHeight="1">
       <c r="A46" s="46" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B46" s="63"/>
       <c r="C46" s="56" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D46" s="64">
         <f t="shared" si="20"/>
@@ -13976,11 +13979,11 @@
     </row>
     <row r="47" spans="1:180" ht="15.75" customHeight="1">
       <c r="A47" s="46" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B47" s="63"/>
       <c r="C47" s="56" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D47" s="62">
         <f t="shared" si="20"/>
@@ -14165,11 +14168,11 @@
     </row>
     <row r="48" spans="1:180" ht="15.75" customHeight="1">
       <c r="A48" s="46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B48" s="63"/>
       <c r="C48" s="61" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D48" s="62">
         <f t="shared" si="20"/>
@@ -14354,11 +14357,11 @@
     </row>
     <row r="49" spans="1:180" ht="15.75" customHeight="1">
       <c r="A49" s="46" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B49" s="63"/>
       <c r="C49" s="61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D49" s="64">
         <f t="shared" si="20"/>
@@ -14543,11 +14546,11 @@
     </row>
     <row r="50" spans="1:180" ht="15.75" customHeight="1">
       <c r="A50" s="46" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B50" s="65"/>
       <c r="C50" s="61" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D50" s="62">
         <f t="shared" si="20"/>
@@ -14732,13 +14735,13 @@
     </row>
     <row r="51" spans="1:180" ht="15.75" customHeight="1">
       <c r="A51" s="46" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B51" s="47">
         <v>27</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D51" s="62">
         <f t="shared" si="20"/>
@@ -14923,13 +14926,13 @@
     </row>
     <row r="52" spans="1:180" ht="15.75" customHeight="1">
       <c r="A52" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B52" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="B52" s="41" t="s">
+      <c r="C52" s="66" t="s">
         <v>272</v>
-      </c>
-      <c r="C52" s="66" t="s">
-        <v>273</v>
       </c>
       <c r="D52" s="49">
         <f>D53+D54+D55+D56+D57</f>
@@ -15135,13 +15138,13 @@
     </row>
     <row r="53" spans="1:180" ht="15.75" customHeight="1">
       <c r="A53" s="46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B53" s="47">
         <v>1</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D53" s="45">
         <f t="shared" ref="D53:D57" si="22">SUM(E53:FX53)</f>
@@ -15326,13 +15329,13 @@
     </row>
     <row r="54" spans="1:180" ht="15.75" customHeight="1">
       <c r="A54" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B54" s="47">
         <v>2</v>
       </c>
       <c r="C54" s="48" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D54" s="45">
         <f t="shared" si="22"/>
@@ -15517,13 +15520,13 @@
     </row>
     <row r="55" spans="1:180" ht="15.75" customHeight="1">
       <c r="A55" s="46" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B55" s="47">
         <v>3</v>
       </c>
       <c r="C55" s="51" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D55" s="45">
         <f t="shared" si="22"/>
@@ -15708,13 +15711,13 @@
     </row>
     <row r="56" spans="1:180" ht="15.75" customHeight="1">
       <c r="A56" s="46" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B56" s="47">
         <v>4</v>
       </c>
       <c r="C56" s="51" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D56" s="45">
         <f t="shared" si="22"/>
@@ -15899,13 +15902,13 @@
     </row>
     <row r="57" spans="1:180" ht="15.75" customHeight="1">
       <c r="A57" s="46" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B57" s="47">
         <v>5</v>
       </c>
       <c r="C57" s="51" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D57" s="71">
         <f t="shared" si="22"/>
@@ -16090,13 +16093,13 @@
     </row>
     <row r="58" spans="1:180" ht="15.75" customHeight="1">
       <c r="A58" s="72" t="s">
+        <v>284</v>
+      </c>
+      <c r="B58" s="41" t="s">
         <v>285</v>
       </c>
-      <c r="B58" s="41" t="s">
+      <c r="C58" s="36" t="s">
         <v>286</v>
-      </c>
-      <c r="C58" s="36" t="s">
-        <v>287</v>
       </c>
       <c r="D58" s="73">
         <f t="shared" ref="D58:FX58" si="23">SUM(D59:D84)-D64-D66-D77-D78-D79</f>
@@ -16809,13 +16812,13 @@
     </row>
     <row r="59" spans="1:180" ht="15.75" customHeight="1">
       <c r="A59" s="46" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B59" s="47">
         <v>1</v>
       </c>
       <c r="C59" s="48" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D59" s="49">
         <f t="shared" ref="D59:D84" si="24">SUM(E59:FX59)</f>
@@ -17000,13 +17003,13 @@
     </row>
     <row r="60" spans="1:180" ht="15.75" customHeight="1">
       <c r="A60" s="46" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B60" s="47">
         <v>2</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D60" s="49">
         <f t="shared" si="24"/>
@@ -17191,13 +17194,13 @@
     </row>
     <row r="61" spans="1:180" ht="15.75" customHeight="1">
       <c r="A61" s="46" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B61" s="47">
         <v>3</v>
       </c>
       <c r="C61" s="51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D61" s="49">
         <f t="shared" si="24"/>
@@ -17382,13 +17385,13 @@
     </row>
     <row r="62" spans="1:180" ht="15.75" customHeight="1">
       <c r="A62" s="46" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B62" s="47">
         <v>4</v>
       </c>
       <c r="C62" s="51" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D62" s="49">
         <f t="shared" si="24"/>
@@ -17573,13 +17576,13 @@
     </row>
     <row r="63" spans="1:180" ht="15.75" customHeight="1">
       <c r="A63" s="46" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B63" s="47">
         <v>5</v>
       </c>
       <c r="C63" s="48" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D63" s="49">
         <f t="shared" si="24"/>
@@ -17764,13 +17767,13 @@
     </row>
     <row r="64" spans="1:180" ht="15.75" customHeight="1">
       <c r="A64" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="B64" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="C64" s="53" t="s">
         <v>294</v>
-      </c>
-      <c r="B64" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="C64" s="53" t="s">
-        <v>295</v>
       </c>
       <c r="D64" s="49">
         <f t="shared" si="24"/>
@@ -17955,13 +17958,13 @@
     </row>
     <row r="65" spans="1:180" ht="15.75" customHeight="1">
       <c r="A65" s="46" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B65" s="47">
         <v>6</v>
       </c>
       <c r="C65" s="51" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D65" s="49">
         <f t="shared" si="24"/>
@@ -18146,13 +18149,13 @@
     </row>
     <row r="66" spans="1:180" ht="15.75" customHeight="1">
       <c r="A66" s="46" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B66" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="C66" s="53" t="s">
         <v>214</v>
-      </c>
-      <c r="C66" s="53" t="s">
-        <v>215</v>
       </c>
       <c r="D66" s="49">
         <f t="shared" si="24"/>
@@ -18337,13 +18340,13 @@
     </row>
     <row r="67" spans="1:180" ht="15.75" customHeight="1">
       <c r="A67" s="46" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B67" s="47">
         <v>7</v>
       </c>
       <c r="C67" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D67" s="49">
         <f t="shared" si="24"/>
@@ -18528,13 +18531,13 @@
     </row>
     <row r="68" spans="1:180" ht="15.75" customHeight="1">
       <c r="A68" s="46" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B68" s="47">
         <v>8</v>
       </c>
       <c r="C68" s="51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D68" s="49">
         <f t="shared" si="24"/>
@@ -18719,13 +18722,13 @@
     </row>
     <row r="69" spans="1:180" ht="15.75" customHeight="1">
       <c r="A69" s="46" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B69" s="47">
         <v>9</v>
       </c>
       <c r="C69" s="51" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D69" s="49">
         <f t="shared" si="24"/>
@@ -18910,13 +18913,13 @@
     </row>
     <row r="70" spans="1:180" ht="15.75" customHeight="1">
       <c r="A70" s="46" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B70" s="47">
         <v>10</v>
       </c>
       <c r="C70" s="51" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D70" s="49">
         <f t="shared" si="24"/>
@@ -19101,13 +19104,13 @@
     </row>
     <row r="71" spans="1:180" ht="15.75" customHeight="1">
       <c r="A71" s="46" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B71" s="47">
         <v>11</v>
       </c>
       <c r="C71" s="51" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D71" s="49">
         <f t="shared" si="24"/>
@@ -19292,13 +19295,13 @@
     </row>
     <row r="72" spans="1:180" ht="15.75" customHeight="1">
       <c r="A72" s="46" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B72" s="47">
         <v>12</v>
       </c>
       <c r="C72" s="51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D72" s="49">
         <f t="shared" si="24"/>
@@ -19483,13 +19486,13 @@
     </row>
     <row r="73" spans="1:180" ht="15.75" customHeight="1">
       <c r="A73" s="46" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B73" s="47">
         <v>13</v>
       </c>
       <c r="C73" s="51" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D73" s="49">
         <f t="shared" si="24"/>
@@ -19674,13 +19677,13 @@
     </row>
     <row r="74" spans="1:180" ht="15.75" customHeight="1">
       <c r="A74" s="46" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B74" s="47">
         <v>14</v>
       </c>
       <c r="C74" s="51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D74" s="49">
         <f t="shared" si="24"/>
@@ -19865,13 +19868,13 @@
     </row>
     <row r="75" spans="1:180" ht="15.75" customHeight="1">
       <c r="A75" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B75" s="47">
         <v>15</v>
       </c>
       <c r="C75" s="51" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D75" s="49">
         <f t="shared" si="24"/>
@@ -20056,13 +20059,13 @@
     </row>
     <row r="76" spans="1:180" ht="15.75" customHeight="1">
       <c r="A76" s="46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B76" s="47">
         <v>16</v>
       </c>
       <c r="C76" s="48" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D76" s="64">
         <f t="shared" si="24"/>
@@ -20247,13 +20250,13 @@
     </row>
     <row r="77" spans="1:180" ht="15.75" customHeight="1">
       <c r="A77" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="B77" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="C77" s="56" t="s">
         <v>308</v>
-      </c>
-      <c r="B77" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="C77" s="56" t="s">
-        <v>309</v>
       </c>
       <c r="D77" s="64">
         <f t="shared" si="24"/>
@@ -20438,11 +20441,11 @@
     </row>
     <row r="78" spans="1:180" ht="15.75" customHeight="1">
       <c r="A78" s="46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B78" s="47"/>
       <c r="C78" s="56" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D78" s="64">
         <f t="shared" si="24"/>
@@ -20627,11 +20630,11 @@
     </row>
     <row r="79" spans="1:180" ht="15.75" customHeight="1">
       <c r="A79" s="46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B79" s="47"/>
       <c r="C79" s="56" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D79" s="64">
         <f t="shared" si="24"/>
@@ -20816,13 +20819,13 @@
     </row>
     <row r="80" spans="1:180" ht="15.75" customHeight="1">
       <c r="A80" s="46" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B80" s="47">
         <v>17</v>
       </c>
       <c r="C80" s="51" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D80" s="64">
         <f t="shared" si="24"/>
@@ -21007,13 +21010,13 @@
     </row>
     <row r="81" spans="1:180" ht="15.75" customHeight="1">
       <c r="A81" s="46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B81" s="47">
         <v>18</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D81" s="64">
         <f t="shared" si="24"/>
@@ -21198,13 +21201,13 @@
     </row>
     <row r="82" spans="1:180" ht="15.75" customHeight="1">
       <c r="A82" s="46" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B82" s="47">
         <v>19</v>
       </c>
       <c r="C82" s="51" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D82" s="64">
         <f t="shared" si="24"/>
@@ -21389,13 +21392,13 @@
     </row>
     <row r="83" spans="1:180" ht="15.75" customHeight="1">
       <c r="A83" s="46" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B83" s="47">
         <v>20</v>
       </c>
       <c r="C83" s="55" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D83" s="62">
         <f t="shared" si="24"/>
@@ -21580,13 +21583,13 @@
     </row>
     <row r="84" spans="1:180" ht="15.75" customHeight="1">
       <c r="A84" s="46" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B84" s="79">
         <v>21</v>
       </c>
       <c r="C84" s="80" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D84" s="81">
         <f t="shared" si="24"/>
@@ -21771,13 +21774,13 @@
     </row>
     <row r="85" spans="1:180" ht="15.75" customHeight="1">
       <c r="A85" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="B85" s="82" t="s">
         <v>319</v>
       </c>
-      <c r="B85" s="82" t="s">
+      <c r="C85" s="83" t="s">
         <v>320</v>
-      </c>
-      <c r="C85" s="83" t="s">
-        <v>321</v>
       </c>
       <c r="D85" s="82"/>
       <c r="E85" s="84"/>
@@ -21959,13 +21962,13 @@
     </row>
     <row r="86" spans="1:180" ht="15.75" customHeight="1">
       <c r="A86" s="46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B86" s="86">
         <v>1</v>
       </c>
       <c r="C86" s="87" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D86" s="40">
         <f t="shared" ref="D86:D105" si="25">SUM(E86:FX86)</f>
@@ -22150,13 +22153,13 @@
     </row>
     <row r="87" spans="1:180" ht="15.75" customHeight="1">
       <c r="A87" s="46" t="s">
+        <v>323</v>
+      </c>
+      <c r="B87" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="C87" s="53" t="s">
         <v>324</v>
-      </c>
-      <c r="B87" s="52" t="s">
-        <v>214</v>
-      </c>
-      <c r="C87" s="53" t="s">
-        <v>325</v>
       </c>
       <c r="D87" s="64">
         <f t="shared" si="25"/>
@@ -22341,13 +22344,13 @@
     </row>
     <row r="88" spans="1:180" ht="15.75" customHeight="1">
       <c r="A88" s="46" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B88" s="47">
         <v>2</v>
       </c>
       <c r="C88" s="122" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D88" s="40">
         <f t="shared" si="25"/>
@@ -22532,11 +22535,11 @@
     </row>
     <row r="89" spans="1:180" ht="15.75" customHeight="1">
       <c r="A89" s="46" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B89" s="47"/>
       <c r="C89" s="56" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D89" s="64">
         <f t="shared" si="25"/>
@@ -22721,11 +22724,11 @@
     </row>
     <row r="90" spans="1:180" ht="15.75" customHeight="1">
       <c r="A90" s="46" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B90" s="47"/>
       <c r="C90" s="56" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D90" s="64">
         <f t="shared" si="25"/>
@@ -22910,13 +22913,13 @@
     </row>
     <row r="91" spans="1:180" ht="15.75" customHeight="1">
       <c r="A91" s="46" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B91" s="47">
         <v>3</v>
       </c>
       <c r="C91" s="123" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D91" s="45">
         <f t="shared" si="25"/>
@@ -23101,11 +23104,11 @@
     </row>
     <row r="92" spans="1:180" ht="15.75" customHeight="1">
       <c r="A92" s="46" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B92" s="47"/>
       <c r="C92" s="56" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D92" s="64">
         <f t="shared" si="25"/>
@@ -23290,11 +23293,11 @@
     </row>
     <row r="93" spans="1:180" ht="15.75" customHeight="1">
       <c r="A93" s="46" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B93" s="47"/>
       <c r="C93" s="56" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D93" s="64">
         <f t="shared" si="25"/>
@@ -23479,13 +23482,13 @@
     </row>
     <row r="94" spans="1:180" ht="15.75" customHeight="1">
       <c r="A94" s="46" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B94" s="47">
         <v>4</v>
       </c>
       <c r="C94" s="124" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D94" s="45">
         <f t="shared" si="25"/>
@@ -23670,13 +23673,13 @@
     </row>
     <row r="95" spans="1:180" ht="15.75" customHeight="1">
       <c r="A95" s="46" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B95" s="47">
         <v>5</v>
       </c>
       <c r="C95" s="48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D95" s="45">
         <f t="shared" si="25"/>
@@ -23861,11 +23864,11 @@
     </row>
     <row r="96" spans="1:180" ht="15.75" customHeight="1">
       <c r="A96" s="46" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B96" s="47"/>
       <c r="C96" s="56" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D96" s="64">
         <f t="shared" si="25"/>
@@ -24050,11 +24053,11 @@
     </row>
     <row r="97" spans="1:180" ht="15.75" customHeight="1">
       <c r="A97" s="46" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B97" s="47"/>
       <c r="C97" s="56" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D97" s="64">
         <f t="shared" si="25"/>
@@ -24239,13 +24242,13 @@
     </row>
     <row r="98" spans="1:180" ht="15.75" customHeight="1">
       <c r="A98" s="46" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B98" s="47">
         <v>6</v>
       </c>
       <c r="C98" s="51" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D98" s="64">
         <f t="shared" si="25"/>
@@ -24430,13 +24433,13 @@
     </row>
     <row r="99" spans="1:180" ht="15.75" customHeight="1">
       <c r="A99" s="46" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B99" s="47">
         <v>7</v>
       </c>
       <c r="C99" s="48" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D99" s="45">
         <f t="shared" si="25"/>
@@ -24621,11 +24624,11 @@
     </row>
     <row r="100" spans="1:180" ht="15.75" customHeight="1">
       <c r="A100" s="46" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B100" s="47"/>
       <c r="C100" s="56" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D100" s="64">
         <f t="shared" si="25"/>
@@ -24810,13 +24813,13 @@
     </row>
     <row r="101" spans="1:180" ht="15.75" customHeight="1">
       <c r="A101" s="46" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B101" s="47">
         <v>8</v>
       </c>
       <c r="C101" s="48" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D101" s="45">
         <f t="shared" si="25"/>
@@ -25001,11 +25004,11 @@
     </row>
     <row r="102" spans="1:180" ht="15.75" customHeight="1">
       <c r="A102" s="46" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B102" s="47"/>
       <c r="C102" s="56" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D102" s="64">
         <f t="shared" si="25"/>
@@ -25190,11 +25193,11 @@
     </row>
     <row r="103" spans="1:180" ht="15.75" customHeight="1">
       <c r="A103" s="46" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B103" s="47"/>
       <c r="C103" s="48" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D103" s="64">
         <f t="shared" si="25"/>
@@ -25379,13 +25382,13 @@
     </row>
     <row r="104" spans="1:180" ht="15.75" customHeight="1">
       <c r="A104" s="46" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B104" s="47">
         <v>9</v>
       </c>
       <c r="C104" s="51" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D104" s="45">
         <f t="shared" si="25"/>
@@ -25570,13 +25573,13 @@
     </row>
     <row r="105" spans="1:180" ht="15.75" customHeight="1">
       <c r="A105" s="46" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B105" s="47">
         <v>10</v>
       </c>
       <c r="C105" s="51" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D105" s="45">
         <f t="shared" si="25"/>
